--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.7384,0.0641,0.0653,0.1064</t>
-  </si>
-  <si>
-    <t>0.0030,0.0048,0.0007,0.9978</t>
-  </si>
-  <si>
-    <t>0.2095,0.2336,0.0249,0.6866</t>
-  </si>
-  <si>
-    <t>0.0165,0.0065,0.0041,0.9895</t>
-  </si>
-  <si>
-    <t>0.9870,0.0093,0.0010,0.0012</t>
-  </si>
-  <si>
-    <t>0.9860,0.0022,0.0002,0.0083</t>
-  </si>
-  <si>
-    <t>0.9878,0.0049,0.0009,0.0028</t>
-  </si>
-  <si>
-    <t>0.9843,0.0068,0.0016,0.0028</t>
-  </si>
-  <si>
-    <t>0.9933,0.0034,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9901,0.0042,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.9879,0.0061,0.0005,0.0022</t>
-  </si>
-  <si>
-    <t>0.9946,0.0018,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.6209,0.0665,0.2003,0.0803</t>
-  </si>
-  <si>
-    <t>0.6274,0.0727,0.3366,0.0287</t>
-  </si>
-  <si>
-    <t>0.5147,0.1487,0.4041,0.0248</t>
-  </si>
-  <si>
-    <t>0.1734,0.0203,0.8654,0.0150</t>
-  </si>
-  <si>
-    <t>0.5714,0.1170,0.3636,0.0470</t>
-  </si>
-  <si>
-    <t>0.0112,0.9783,0.0108,0.0010</t>
-  </si>
-  <si>
-    <t>0.0357,0.9540,0.0125,0.0012</t>
-  </si>
-  <si>
-    <t>0.3484,0.7525,0.0111,0.0012</t>
-  </si>
-  <si>
-    <t>0.1011,0.8946,0.0329,0.0017</t>
-  </si>
-  <si>
-    <t>0.0107,0.9795,0.0101,0.0005</t>
-  </si>
-  <si>
-    <t>0.3475,0.0533,0.5421,0.1206</t>
-  </si>
-  <si>
-    <t>0.3874,0.1093,0.5555,0.0744</t>
-  </si>
-  <si>
-    <t>0.0158,0.0066,0.8873,0.2750</t>
-  </si>
-  <si>
-    <t>0.4503,0.0359,0.6464,0.0160</t>
-  </si>
-  <si>
-    <t>0.1523,0.0112,0.8764,0.0411</t>
-  </si>
-  <si>
-    <t>0.2703,0.0198,0.6801,0.1260</t>
-  </si>
-  <si>
-    <t>0.0041,0.0024,0.9866,0.0263</t>
-  </si>
-  <si>
-    <t>0.6032,0.3455,0.1012,0.0196</t>
-  </si>
-  <si>
-    <t>0.6799,0.0694,0.3256,0.0193</t>
-  </si>
-  <si>
-    <t>0.0013,0.0159,0.9867,0.0172</t>
-  </si>
-  <si>
-    <t>0.1682,0.7212,0.1216,0.0034</t>
-  </si>
-  <si>
-    <t>0.7583,0.1120,0.0591,0.0586</t>
-  </si>
-  <si>
-    <t>0.5700,0.4991,0.0238,0.0161</t>
-  </si>
-  <si>
-    <t>0.6314,0.4355,0.0392,0.0020</t>
-  </si>
-  <si>
-    <t>0.0617,0.8912,0.2313,0.0036</t>
-  </si>
-  <si>
-    <t>0.0221,0.6881,0.6446,0.0196</t>
-  </si>
-  <si>
-    <t>0.0300,0.0678,0.8885,0.0503</t>
-  </si>
-  <si>
-    <t>0.0223,0.2056,0.8914,0.0137</t>
-  </si>
-  <si>
-    <t>0.0491,0.0695,0.8798,0.0313</t>
-  </si>
-  <si>
-    <t>0.0013,0.0135,0.9943,0.0010</t>
-  </si>
-  <si>
-    <t>0.0045,0.9529,0.4481,0.0018</t>
-  </si>
-  <si>
-    <t>0.0437,0.0800,0.9117,0.0105</t>
-  </si>
-  <si>
-    <t>0.0439,0.7730,0.0318,0.5512</t>
-  </si>
-  <si>
-    <t>0.0009,0.9895,0.0159,0.0172</t>
-  </si>
-  <si>
-    <t>0.0026,0.9844,0.0407,0.0084</t>
-  </si>
-  <si>
-    <t>0.0020,0.9870,0.0996,0.0012</t>
-  </si>
-  <si>
-    <t>0.0017,0.2522,0.9685,0.0035</t>
-  </si>
-  <si>
-    <t>0.0044,0.4858,0.9438,0.0005</t>
-  </si>
-  <si>
-    <t>0.0542,0.0439,0.8992,0.0345</t>
-  </si>
-  <si>
-    <t>0.0059,0.0013,0.9918,0.0053</t>
-  </si>
-  <si>
-    <t>0.0019,0.0128,0.9935,0.0034</t>
-  </si>
-  <si>
-    <t>0.0092,0.0245,0.9792,0.0022</t>
-  </si>
-  <si>
-    <t>0.9572,0.0446,0.0040,0.0035</t>
-  </si>
-  <si>
-    <t>0.9575,0.0242,0.0061,0.0078</t>
-  </si>
-  <si>
-    <t>0.8877,0.1524,0.0058,0.0044</t>
-  </si>
-  <si>
-    <t>0.0176,0.0304,0.9787,0.0043</t>
-  </si>
-  <si>
-    <t>0.9831,0.0147,0.0008,0.0018</t>
-  </si>
-  <si>
-    <t>0.9896,0.0044,0.0004,0.0017</t>
-  </si>
-  <si>
-    <t>0.9600,0.0332,0.0026,0.0052</t>
-  </si>
-  <si>
-    <t>0.0083,0.5472,0.9193,0.0016</t>
-  </si>
-  <si>
-    <t>0.0005,0.0238,0.9896,0.0040</t>
-  </si>
-  <si>
-    <t>0.0021,0.1744,0.6226,0.2153</t>
-  </si>
-  <si>
-    <t>0.0017,0.7829,0.9304,0.0002</t>
-  </si>
-  <si>
-    <t>0.0092,0.0101,0.9824,0.0045</t>
-  </si>
-  <si>
-    <t>0.0238,0.9176,0.1406,0.0017</t>
-  </si>
-  <si>
-    <t>0.0016,0.9928,0.0119,0.0006</t>
-  </si>
-  <si>
-    <t>0.8005,0.0669,0.2058,0.0054</t>
-  </si>
-  <si>
-    <t>0.6283,0.2500,0.1946,0.0172</t>
-  </si>
-  <si>
-    <t>0.0243,0.0336,0.9516,0.0126</t>
-  </si>
-  <si>
-    <t>0.0007,0.9398,0.8458,0.0006</t>
-  </si>
-  <si>
-    <t>0.0030,0.9204,0.7513,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.9859,0.2391,0.0028</t>
-  </si>
-  <si>
-    <t>0.0005,0.9771,0.6849,0.0006</t>
-  </si>
-  <si>
-    <t>0.0150,0.0043,0.0141,0.9847</t>
-  </si>
-  <si>
-    <t>0.0035,0.0020,0.0011,0.9975</t>
-  </si>
-  <si>
-    <t>0.0015,0.0011,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0090,0.0046,0.0050,0.9928</t>
-  </si>
-  <si>
-    <t>0.0063,0.0171,0.0048,0.9931</t>
-  </si>
-  <si>
-    <t>0.0022,0.0034,0.0008,0.9982</t>
-  </si>
-  <si>
-    <t>0.0004,0.9087,0.9293,0.0003</t>
-  </si>
-  <si>
-    <t>0.0008,0.8039,0.9674,0.0001</t>
-  </si>
-  <si>
-    <t>0.0103,0.5385,0.8708,0.0043</t>
-  </si>
-  <si>
-    <t>0.0146,0.3181,0.9160,0.0022</t>
-  </si>
-  <si>
-    <t>0.0015,0.9437,0.7886,0.0002</t>
-  </si>
-  <si>
-    <t>0.0128,0.7243,0.7539,0.0041</t>
-  </si>
-  <si>
-    <t>0.9924,0.0030,0.0007,0.0014</t>
-  </si>
-  <si>
-    <t>0.9935,0.0032,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9883,0.0060,0.0007,0.0015</t>
-  </si>
-  <si>
-    <t>0.9724,0.0101,0.0011,0.0088</t>
-  </si>
-  <si>
-    <t>0.9660,0.0363,0.0050,0.0018</t>
-  </si>
-  <si>
-    <t>0.9886,0.0044,0.0006,0.0024</t>
-  </si>
-  <si>
-    <t>0.9719,0.0262,0.0044,0.0020</t>
-  </si>
-  <si>
-    <t>0.9830,0.0087,0.0004,0.0033</t>
-  </si>
-  <si>
-    <t>0.9945,0.0016,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9931,0.0030,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.9909,0.0015,0.0001,0.0041</t>
-  </si>
-  <si>
-    <t>0.9930,0.0014,0.0001,0.0026</t>
-  </si>
-  <si>
-    <t>0.9905,0.0042,0.0004,0.0019</t>
-  </si>
-  <si>
-    <t>0.9868,0.0065,0.0006,0.0024</t>
-  </si>
-  <si>
-    <t>0.9892,0.0067,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9876,0.0009,0.0001,0.0091</t>
-  </si>
-  <si>
-    <t>0.0058,0.0097,0.9753,0.0353</t>
-  </si>
-  <si>
-    <t>0.1184,0.0765,0.8367,0.0228</t>
-  </si>
-  <si>
-    <t>0.2651,0.1081,0.3278,0.4464</t>
-  </si>
-  <si>
-    <t>0.2078,0.0461,0.8245,0.0055</t>
-  </si>
-  <si>
-    <t>0.0647,0.9299,0.0144,0.0010</t>
-  </si>
-  <si>
-    <t>0.0106,0.9770,0.0062,0.0023</t>
-  </si>
-  <si>
-    <t>0.0942,0.9228,0.0025,0.0034</t>
-  </si>
-  <si>
-    <t>0.1556,0.8475,0.0234,0.0032</t>
-  </si>
-  <si>
-    <t>0.0109,0.9735,0.0063,0.0035</t>
-  </si>
-  <si>
-    <t>0.0080,0.9810,0.0042,0.0011</t>
-  </si>
-  <si>
-    <t>0.4758,0.6318,0.0184,0.0024</t>
-  </si>
-  <si>
-    <t>0.5971,0.0956,0.2900,0.0398</t>
-  </si>
-  <si>
-    <t>0.4289,0.1367,0.4758,0.0583</t>
-  </si>
-  <si>
-    <t>0.3243,0.4696,0.1752,0.1105</t>
-  </si>
-  <si>
-    <t>0.4678,0.0227,0.6123,0.0291</t>
-  </si>
-  <si>
-    <t>0.0709,0.0699,0.0759,0.9103</t>
-  </si>
-  <si>
-    <t>0.0005,0.9959,0.0122,0.0018</t>
-  </si>
-  <si>
-    <t>0.0033,0.9711,0.0906,0.0299</t>
-  </si>
-  <si>
-    <t>0.0675,0.8374,0.1335,0.0499</t>
-  </si>
-  <si>
-    <t>0.0004,0.9569,0.8624,0.0003</t>
-  </si>
-  <si>
-    <t>0.0292,0.9573,0.0770,0.0008</t>
-  </si>
-  <si>
-    <t>0.8433,0.1333,0.0516,0.0085</t>
-  </si>
-  <si>
-    <t>0.3822,0.6962,0.0379,0.0045</t>
-  </si>
-  <si>
-    <t>0.9838,0.0078,0.0011,0.0031</t>
-  </si>
-  <si>
-    <t>0.9903,0.0027,0.0006,0.0026</t>
-  </si>
-  <si>
-    <t>0.9682,0.0079,0.0013,0.0137</t>
-  </si>
-  <si>
-    <t>0.9814,0.0032,0.0014,0.0067</t>
-  </si>
-  <si>
-    <t>0.9901,0.0021,0.0002,0.0042</t>
-  </si>
-  <si>
-    <t>0.9244,0.0402,0.0207,0.0106</t>
-  </si>
-  <si>
-    <t>0.9713,0.0134,0.0030,0.0050</t>
-  </si>
-  <si>
-    <t>0.9845,0.0034,0.0013,0.0057</t>
-  </si>
-  <si>
-    <t>0.0009,0.8892,0.8918,0.0001</t>
-  </si>
-  <si>
-    <t>0.0086,0.4505,0.9293,0.0025</t>
-  </si>
-  <si>
-    <t>0.0261,0.4186,0.8084,0.0054</t>
-  </si>
-  <si>
-    <t>0.0090,0.0344,0.9749,0.0040</t>
-  </si>
-  <si>
-    <t>0.5412,0.0665,0.1161,0.1946</t>
-  </si>
-  <si>
-    <t>0.5383,0.2195,0.2333,0.0804</t>
-  </si>
-  <si>
-    <t>0.3588,0.0360,0.6342,0.1106</t>
-  </si>
-  <si>
-    <t>0.5122,0.2894,0.1507,0.0877</t>
-  </si>
-  <si>
-    <t>0.0849,0.0173,0.0206,0.9456</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.0031,0.0055,0.0008,0.9975</t>
-  </si>
-  <si>
-    <t>0.0011,0.0018,0.0011,0.9987</t>
-  </si>
-  <si>
-    <t>0.0004,0.9828,0.4727,0.0013</t>
-  </si>
-  <si>
-    <t>0.9775,0.0099,0.0023,0.0041</t>
-  </si>
-  <si>
-    <t>0.4952,0.5506,0.0129,0.0241</t>
-  </si>
-  <si>
-    <t>0.9425,0.0093,0.0008,0.0453</t>
-  </si>
-  <si>
-    <t>0.9398,0.0607,0.0025,0.0052</t>
-  </si>
-  <si>
-    <t>0.9000,0.0462,0.0122,0.0337</t>
-  </si>
-  <si>
-    <t>0.6709,0.0385,0.1371,0.1659</t>
-  </si>
-  <si>
-    <t>0.9502,0.0109,0.0033,0.0267</t>
-  </si>
-  <si>
-    <t>0.0002,0.0296,0.9962,0.0010</t>
-  </si>
-  <si>
-    <t>0.7567,0.0058,0.0429,0.2013</t>
-  </si>
-  <si>
-    <t>0.9051,0.0340,0.0246,0.0168</t>
-  </si>
-  <si>
-    <t>0.3698,0.6779,0.0329,0.0063</t>
-  </si>
-  <si>
-    <t>0.7505,0.1775,0.0444,0.0383</t>
-  </si>
-  <si>
-    <t>0.4558,0.6060,0.0423,0.0103</t>
-  </si>
-  <si>
-    <t>0.7088,0.1438,0.0378,0.1067</t>
-  </si>
-  <si>
-    <t>0.5727,0.2690,0.2018,0.0084</t>
-  </si>
-  <si>
-    <t>0.8167,0.1405,0.0391,0.0131</t>
-  </si>
-  <si>
-    <t>0.9820,0.0059,0.0015,0.0052</t>
-  </si>
-  <si>
-    <t>0.9759,0.0067,0.0004,0.0118</t>
-  </si>
-  <si>
-    <t>0.9824,0.0052,0.0004,0.0048</t>
-  </si>
-  <si>
-    <t>0.9703,0.0016,0.0005,0.0267</t>
-  </si>
-  <si>
-    <t>0.9805,0.0151,0.0010,0.0021</t>
-  </si>
-  <si>
-    <t>0.9706,0.0180,0.0013,0.0043</t>
-  </si>
-  <si>
-    <t>0.9862,0.0025,0.0002,0.0061</t>
-  </si>
-  <si>
-    <t>0.9844,0.0035,0.0008,0.0053</t>
-  </si>
-  <si>
-    <t>0.6198,0.4457,0.0441,0.0097</t>
-  </si>
-  <si>
-    <t>0.8211,0.2848,0.0111,0.0014</t>
-  </si>
-  <si>
-    <t>0.6419,0.4790,0.0185,0.0018</t>
-  </si>
-  <si>
-    <t>0.7062,0.1790,0.1784,0.0059</t>
-  </si>
-  <si>
-    <t>0.9274,0.1368,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.9233,0.0646,0.0189,0.0035</t>
-  </si>
-  <si>
-    <t>0.9785,0.0212,0.0030,0.0012</t>
-  </si>
-  <si>
-    <t>0.9399,0.0626,0.0119,0.0032</t>
-  </si>
-  <si>
-    <t>0.0098,0.0290,0.9803,0.0039</t>
-  </si>
-  <si>
-    <t>0.9455,0.0638,0.0079,0.0021</t>
-  </si>
-  <si>
-    <t>0.0167,0.0039,0.9815,0.0048</t>
-  </si>
-  <si>
-    <t>0.0039,0.0467,0.9795,0.0048</t>
-  </si>
-  <si>
-    <t>0.0197,0.0031,0.9855,0.0026</t>
-  </si>
-  <si>
-    <t>0.0010,0.1203,0.9896,0.0013</t>
-  </si>
-  <si>
-    <t>0.0622,0.0319,0.9201,0.0080</t>
-  </si>
-  <si>
-    <t>0.0188,0.0145,0.9730,0.0059</t>
-  </si>
-  <si>
-    <t>0.0221,0.0057,0.9781,0.0059</t>
-  </si>
-  <si>
-    <t>0.3115,0.0572,0.7150,0.0349</t>
-  </si>
-  <si>
-    <t>0.4363,0.0744,0.4890,0.1301</t>
-  </si>
-  <si>
-    <t>0.5365,0.1174,0.4330,0.0283</t>
-  </si>
-  <si>
-    <t>0.4727,0.1492,0.4164,0.0722</t>
-  </si>
-  <si>
-    <t>0.0799,0.5362,0.5867,0.0148</t>
-  </si>
-  <si>
-    <t>0.4557,0.1050,0.4618,0.1085</t>
-  </si>
-  <si>
-    <t>0.5368,0.2515,0.1870,0.0677</t>
-  </si>
-  <si>
-    <t>0.5997,0.0619,0.3825,0.0480</t>
-  </si>
-  <si>
-    <t>0.6479,0.4706,0.0061,0.0051</t>
-  </si>
-  <si>
-    <t>0.8678,0.1920,0.0142,0.0027</t>
-  </si>
-  <si>
-    <t>0.9071,0.1414,0.0030,0.0029</t>
-  </si>
-  <si>
-    <t>0.9674,0.0264,0.0043,0.0024</t>
-  </si>
-  <si>
-    <t>0.7496,0.3853,0.0080,0.0032</t>
-  </si>
-  <si>
-    <t>0.5250,0.2272,0.2442,0.0522</t>
-  </si>
-  <si>
-    <t>0.4699,0.0381,0.6001,0.0328</t>
-  </si>
-  <si>
-    <t>0.3804,0.1417,0.1601,0.4376</t>
-  </si>
-  <si>
-    <t>0.4159,0.0487,0.2881,0.2451</t>
-  </si>
-  <si>
-    <t>0.4023,0.0894,0.5977,0.0235</t>
-  </si>
-  <si>
-    <t>0.0132,0.0212,0.9538,0.0521</t>
-  </si>
-  <si>
-    <t>0.0082,0.0520,0.9430,0.0330</t>
-  </si>
-  <si>
-    <t>0.0616,0.1752,0.8185,0.0289</t>
-  </si>
-  <si>
-    <t>0.0669,0.2929,0.7467,0.0098</t>
-  </si>
-  <si>
-    <t>0.0165,0.4946,0.8249,0.0042</t>
-  </si>
-  <si>
-    <t>0.9419,0.0392,0.0025,0.0099</t>
-  </si>
-  <si>
-    <t>0.9764,0.0135,0.0037,0.0032</t>
-  </si>
-  <si>
-    <t>0.9782,0.0145,0.0004,0.0034</t>
-  </si>
-  <si>
-    <t>0.9891,0.0062,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.9464,0.0392,0.0007,0.0066</t>
-  </si>
-  <si>
-    <t>0.9954,0.0016,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9870,0.0089,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9746,0.0117,0.0032,0.0050</t>
-  </si>
-  <si>
-    <t>0.1639,0.0208,0.8788,0.0141</t>
-  </si>
-  <si>
-    <t>0.5824,0.2042,0.2739,0.0366</t>
-  </si>
-  <si>
-    <t>0.6150,0.2097,0.0110,0.1498</t>
-  </si>
-  <si>
-    <t>0.0087,0.0431,0.9648,0.0087</t>
-  </si>
-  <si>
-    <t>0.0002,0.0648,0.9940,0.0011</t>
-  </si>
-  <si>
-    <t>0.0382,0.0750,0.9065,0.0155</t>
-  </si>
-  <si>
-    <t>0.0025,0.0109,0.9820,0.0171</t>
-  </si>
-  <si>
-    <t>0.1268,0.0774,0.7868,0.0329</t>
-  </si>
-  <si>
-    <t>0.0008,0.0212,0.9863,0.0097</t>
-  </si>
-  <si>
-    <t>0.0373,0.0473,0.9263,0.0201</t>
-  </si>
-  <si>
-    <t>0.1214,0.0812,0.8276,0.0250</t>
-  </si>
-  <si>
-    <t>0.5669,0.0475,0.4037,0.0466</t>
-  </si>
-  <si>
-    <t>0.3792,0.0127,0.7114,0.0352</t>
-  </si>
-  <si>
-    <t>0.4156,0.0404,0.0543,0.5359</t>
-  </si>
-  <si>
-    <t>0.9785,0.0112,0.0014,0.0040</t>
-  </si>
-  <si>
-    <t>0.9876,0.0048,0.0004,0.0030</t>
-  </si>
-  <si>
-    <t>0.9914,0.0052,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9865,0.0130,0.0014,0.0010</t>
-  </si>
-  <si>
-    <t>0.9741,0.0153,0.0012,0.0056</t>
-  </si>
-  <si>
-    <t>0.9859,0.0049,0.0003,0.0038</t>
-  </si>
-  <si>
-    <t>0.9925,0.0016,0.0004,0.0026</t>
-  </si>
-  <si>
-    <t>0.9744,0.0135,0.0031,0.0042</t>
-  </si>
-  <si>
-    <t>0.0116,0.3992,0.8749,0.0011</t>
-  </si>
-  <si>
-    <t>0.0124,0.1519,0.9486,0.0042</t>
-  </si>
-  <si>
-    <t>0.0145,0.0557,0.9524,0.0142</t>
-  </si>
-  <si>
-    <t>0.3224,0.1520,0.5510,0.0277</t>
-  </si>
-  <si>
-    <t>0.0072,0.0057,0.9801,0.0122</t>
-  </si>
-  <si>
-    <t>0.1120,0.0521,0.2725,0.7480</t>
-  </si>
-  <si>
-    <t>0.0788,0.0103,0.9225,0.0220</t>
-  </si>
-  <si>
-    <t>0.0264,0.0185,0.9275,0.0356</t>
-  </si>
-  <si>
-    <t>0.4000,0.0019,0.0072,0.7759</t>
-  </si>
-  <si>
-    <t>0.0408,0.0805,0.0127,0.9596</t>
-  </si>
-  <si>
-    <t>0.0109,0.0045,0.0121,0.9877</t>
-  </si>
-  <si>
-    <t>0.0006,0.0018,0.0004,0.9994</t>
-  </si>
-  <si>
-    <t>0.0007,0.0008,0.0008,0.9991</t>
-  </si>
-  <si>
-    <t>0.1548,0.0625,0.0042,0.8729</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.5066,0.1243,0.1717,0.2469</t>
+  </si>
+  <si>
+    <t>0.0167,0.0090,0.0014,0.9904</t>
+  </si>
+  <si>
+    <t>0.0955,0.0126,0.0009,0.9583</t>
+  </si>
+  <si>
+    <t>0.2031,0.0438,0.0139,0.8729</t>
+  </si>
+  <si>
+    <t>0.9954,0.0014,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9820,0.0086,0.0002,0.0040</t>
+  </si>
+  <si>
+    <t>0.9880,0.0084,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9901,0.0059,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.9867,0.0025,0.0002,0.0054</t>
+  </si>
+  <si>
+    <t>0.9792,0.0071,0.0014,0.0059</t>
+  </si>
+  <si>
+    <t>0.9770,0.0206,0.0009,0.0028</t>
+  </si>
+  <si>
+    <t>0.9893,0.0063,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.5989,0.0760,0.2577,0.0712</t>
+  </si>
+  <si>
+    <t>0.2474,0.0491,0.7864,0.0206</t>
+  </si>
+  <si>
+    <t>0.5181,0.0222,0.6610,0.0097</t>
+  </si>
+  <si>
+    <t>0.3099,0.0982,0.6319,0.0374</t>
+  </si>
+  <si>
+    <t>0.6022,0.0912,0.2992,0.0507</t>
+  </si>
+  <si>
+    <t>0.0095,0.9832,0.0115,0.0006</t>
+  </si>
+  <si>
+    <t>0.0232,0.9629,0.0115,0.0018</t>
+  </si>
+  <si>
+    <t>0.0863,0.9246,0.0139,0.0007</t>
+  </si>
+  <si>
+    <t>0.0431,0.9512,0.0088,0.0011</t>
+  </si>
+  <si>
+    <t>0.0048,0.9887,0.0092,0.0003</t>
+  </si>
+  <si>
+    <t>0.3901,0.0423,0.3164,0.2414</t>
+  </si>
+  <si>
+    <t>0.2882,0.3286,0.3866,0.1059</t>
+  </si>
+  <si>
+    <t>0.0474,0.0238,0.9419,0.0059</t>
+  </si>
+  <si>
+    <t>0.1915,0.1923,0.4146,0.2977</t>
+  </si>
+  <si>
+    <t>0.0733,0.0142,0.9435,0.0059</t>
+  </si>
+  <si>
+    <t>0.1036,0.0294,0.8180,0.0932</t>
+  </si>
+  <si>
+    <t>0.0131,0.0047,0.9691,0.0304</t>
+  </si>
+  <si>
+    <t>0.2718,0.7261,0.0443,0.0050</t>
+  </si>
+  <si>
+    <t>0.4854,0.0359,0.5603,0.0443</t>
+  </si>
+  <si>
+    <t>0.0292,0.0676,0.9462,0.0195</t>
+  </si>
+  <si>
+    <t>0.0723,0.8694,0.1628,0.0058</t>
+  </si>
+  <si>
+    <t>0.6811,0.3087,0.0593,0.0257</t>
+  </si>
+  <si>
+    <t>0.2343,0.0678,0.7832,0.0316</t>
+  </si>
+  <si>
+    <t>0.7065,0.3316,0.0505,0.0030</t>
+  </si>
+  <si>
+    <t>0.0215,0.9564,0.1745,0.0009</t>
+  </si>
+  <si>
+    <t>0.0124,0.7616,0.6374,0.0232</t>
+  </si>
+  <si>
+    <t>0.0366,0.1022,0.8890,0.0331</t>
+  </si>
+  <si>
+    <t>0.0089,0.0292,0.9251,0.0558</t>
+  </si>
+  <si>
+    <t>0.1499,0.0157,0.8151,0.0711</t>
+  </si>
+  <si>
+    <t>0.0086,0.4828,0.9029,0.0020</t>
+  </si>
+  <si>
+    <t>0.0048,0.9731,0.1610,0.0034</t>
+  </si>
+  <si>
+    <t>0.0088,0.0333,0.9004,0.1065</t>
+  </si>
+  <si>
+    <t>0.0735,0.5603,0.0144,0.7343</t>
+  </si>
+  <si>
+    <t>0.0007,0.9909,0.0150,0.0163</t>
+  </si>
+  <si>
+    <t>0.0039,0.9759,0.0697,0.0081</t>
+  </si>
+  <si>
+    <t>0.0012,0.9816,0.2582,0.0033</t>
+  </si>
+  <si>
+    <t>0.0009,0.0366,0.9772,0.0153</t>
+  </si>
+  <si>
+    <t>0.0138,0.1490,0.9552,0.0020</t>
+  </si>
+  <si>
+    <t>0.0471,0.0166,0.9248,0.0372</t>
+  </si>
+  <si>
+    <t>0.0514,0.0066,0.9094,0.0789</t>
+  </si>
+  <si>
+    <t>0.0030,0.0124,0.9866,0.0091</t>
+  </si>
+  <si>
+    <t>0.0110,0.0103,0.9782,0.0058</t>
+  </si>
+  <si>
+    <t>0.9132,0.0881,0.0109,0.0067</t>
+  </si>
+  <si>
+    <t>0.9526,0.0255,0.0050,0.0139</t>
+  </si>
+  <si>
+    <t>0.9784,0.0106,0.0052,0.0028</t>
+  </si>
+  <si>
+    <t>0.0225,0.0390,0.9630,0.0159</t>
+  </si>
+  <si>
+    <t>0.9759,0.0151,0.0040,0.0025</t>
+  </si>
+  <si>
+    <t>0.9865,0.0060,0.0010,0.0029</t>
+  </si>
+  <si>
+    <t>0.9729,0.0307,0.0029,0.0014</t>
+  </si>
+  <si>
+    <t>0.0005,0.9427,0.8912,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.1710,0.9840,0.0020</t>
+  </si>
+  <si>
+    <t>0.0276,0.0603,0.8622,0.0926</t>
+  </si>
+  <si>
+    <t>0.0021,0.5862,0.9674,0.0003</t>
+  </si>
+  <si>
+    <t>0.0146,0.0068,0.9779,0.0066</t>
+  </si>
+  <si>
+    <t>0.0169,0.9386,0.0518,0.0042</t>
+  </si>
+  <si>
+    <t>0.0006,0.9956,0.0054,0.0009</t>
+  </si>
+  <si>
+    <t>0.8847,0.0474,0.0536,0.0086</t>
+  </si>
+  <si>
+    <t>0.3259,0.5507,0.2209,0.0068</t>
+  </si>
+  <si>
+    <t>0.0185,0.0424,0.9615,0.0136</t>
+  </si>
+  <si>
+    <t>0.0015,0.9269,0.8527,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.9381,0.8875,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9795,0.2058,0.0064</t>
+  </si>
+  <si>
+    <t>0.0014,0.9668,0.6296,0.0009</t>
+  </si>
+  <si>
+    <t>0.0077,0.0035,0.0047,0.9933</t>
+  </si>
+  <si>
+    <t>0.0011,0.0389,0.0003,0.9976</t>
+  </si>
+  <si>
+    <t>0.0073,0.0094,0.0031,0.9932</t>
+  </si>
+  <si>
+    <t>0.0134,0.0073,0.0023,0.9925</t>
+  </si>
+  <si>
+    <t>0.0112,0.0204,0.0080,0.9882</t>
+  </si>
+  <si>
+    <t>0.0016,0.0024,0.0020,0.9979</t>
+  </si>
+  <si>
+    <t>0.0009,0.9382,0.8287,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.3514,0.9873,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.6752,0.9033,0.0003</t>
+  </si>
+  <si>
+    <t>0.0057,0.4229,0.9450,0.0007</t>
+  </si>
+  <si>
+    <t>0.0032,0.6946,0.9356,0.0007</t>
+  </si>
+  <si>
+    <t>0.0107,0.6889,0.7549,0.0014</t>
+  </si>
+  <si>
+    <t>0.9883,0.0042,0.0005,0.0025</t>
+  </si>
+  <si>
+    <t>0.9864,0.0065,0.0004,0.0024</t>
+  </si>
+  <si>
+    <t>0.9860,0.0169,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9823,0.0046,0.0017,0.0054</t>
+  </si>
+  <si>
+    <t>0.9825,0.0041,0.0003,0.0064</t>
+  </si>
+  <si>
+    <t>0.9926,0.0020,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9886,0.0080,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9890,0.0028,0.0004,0.0040</t>
+  </si>
+  <si>
+    <t>0.9907,0.0027,0.0002,0.0026</t>
+  </si>
+  <si>
+    <t>0.9945,0.0013,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9939,0.0014,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9927,0.0032,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9807,0.0042,0.0003,0.0088</t>
+  </si>
+  <si>
+    <t>0.9919,0.0019,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.9887,0.0044,0.0007,0.0026</t>
+  </si>
+  <si>
+    <t>0.9908,0.0025,0.0004,0.0032</t>
+  </si>
+  <si>
+    <t>0.0020,0.0017,0.9852,0.0656</t>
+  </si>
+  <si>
+    <t>0.0638,0.0611,0.8969,0.0141</t>
+  </si>
+  <si>
+    <t>0.0455,0.0138,0.1019,0.9229</t>
+  </si>
+  <si>
+    <t>0.1875,0.0303,0.8388,0.0197</t>
+  </si>
+  <si>
+    <t>0.0322,0.9551,0.0254,0.0031</t>
+  </si>
+  <si>
+    <t>0.0918,0.8836,0.0398,0.0021</t>
+  </si>
+  <si>
+    <t>0.1520,0.8825,0.0070,0.0036</t>
+  </si>
+  <si>
+    <t>0.1460,0.8613,0.0168,0.0040</t>
+  </si>
+  <si>
+    <t>0.0957,0.8892,0.0220,0.0051</t>
+  </si>
+  <si>
+    <t>0.0067,0.9826,0.0083,0.0012</t>
+  </si>
+  <si>
+    <t>0.6553,0.4705,0.0122,0.0034</t>
+  </si>
+  <si>
+    <t>0.5044,0.2209,0.3364,0.0475</t>
+  </si>
+  <si>
+    <t>0.4313,0.0344,0.5716,0.0704</t>
+  </si>
+  <si>
+    <t>0.2460,0.4989,0.1230,0.2404</t>
+  </si>
+  <si>
+    <t>0.4325,0.1473,0.4954,0.0392</t>
+  </si>
+  <si>
+    <t>0.0209,0.0867,0.0071,0.9727</t>
+  </si>
+  <si>
+    <t>0.0010,0.9923,0.0338,0.0027</t>
+  </si>
+  <si>
+    <t>0.0045,0.9765,0.1275,0.0025</t>
+  </si>
+  <si>
+    <t>0.0862,0.7524,0.0357,0.2193</t>
+  </si>
+  <si>
+    <t>0.0001,0.9508,0.9335,0.0001</t>
+  </si>
+  <si>
+    <t>0.0209,0.9623,0.1136,0.0007</t>
+  </si>
+  <si>
+    <t>0.7019,0.3412,0.0489,0.0063</t>
+  </si>
+  <si>
+    <t>0.6285,0.3812,0.0568,0.0028</t>
+  </si>
+  <si>
+    <t>0.9881,0.0066,0.0010,0.0016</t>
+  </si>
+  <si>
+    <t>0.9807,0.0017,0.0006,0.0151</t>
+  </si>
+  <si>
+    <t>0.9732,0.0103,0.0016,0.0086</t>
+  </si>
+  <si>
+    <t>0.9704,0.0126,0.0081,0.0036</t>
+  </si>
+  <si>
+    <t>0.9921,0.0026,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9663,0.0215,0.0034,0.0047</t>
+  </si>
+  <si>
+    <t>0.9734,0.0138,0.0048,0.0037</t>
+  </si>
+  <si>
+    <t>0.9775,0.0053,0.0039,0.0065</t>
+  </si>
+  <si>
+    <t>0.0024,0.6452,0.9540,0.0009</t>
+  </si>
+  <si>
+    <t>0.0068,0.7225,0.8122,0.0011</t>
+  </si>
+  <si>
+    <t>0.0138,0.1170,0.9565,0.0028</t>
+  </si>
+  <si>
+    <t>0.0251,0.1683,0.9087,0.0023</t>
+  </si>
+  <si>
+    <t>0.4192,0.0837,0.3376,0.2353</t>
+  </si>
+  <si>
+    <t>0.5800,0.2098,0.2079,0.0372</t>
+  </si>
+  <si>
+    <t>0.6028,0.0335,0.4981,0.0181</t>
+  </si>
+  <si>
+    <t>0.3379,0.4551,0.1945,0.0393</t>
+  </si>
+  <si>
+    <t>0.0554,0.0131,0.0118,0.9700</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0038,0.0053,0.0025,0.9956</t>
+  </si>
+  <si>
+    <t>0.0030,0.0008,0.0008,0.9980</t>
+  </si>
+  <si>
+    <t>0.0009,0.9538,0.7942,0.0007</t>
+  </si>
+  <si>
+    <t>0.9444,0.0057,0.0099,0.0303</t>
+  </si>
+  <si>
+    <t>0.5274,0.5891,0.0117,0.0047</t>
+  </si>
+  <si>
+    <t>0.8281,0.0131,0.0017,0.1681</t>
+  </si>
+  <si>
+    <t>0.9257,0.1019,0.0067,0.0020</t>
+  </si>
+  <si>
+    <t>0.9608,0.0055,0.0055,0.0195</t>
+  </si>
+  <si>
+    <t>0.6108,0.1949,0.2657,0.0410</t>
+  </si>
+  <si>
+    <t>0.9450,0.0137,0.0244,0.0100</t>
+  </si>
+  <si>
+    <t>0.0002,0.0324,0.9862,0.0112</t>
+  </si>
+  <si>
+    <t>0.7100,0.0083,0.0331,0.2292</t>
+  </si>
+  <si>
+    <t>0.9149,0.0335,0.0073,0.0320</t>
+  </si>
+  <si>
+    <t>0.5820,0.4116,0.0839,0.0239</t>
+  </si>
+  <si>
+    <t>0.8122,0.1835,0.0319,0.0112</t>
+  </si>
+  <si>
+    <t>0.8640,0.0652,0.0916,0.0053</t>
+  </si>
+  <si>
+    <t>0.0935,0.8641,0.0187,0.0291</t>
+  </si>
+  <si>
+    <t>0.6742,0.2264,0.1373,0.0076</t>
+  </si>
+  <si>
+    <t>0.6947,0.3049,0.0415,0.0159</t>
+  </si>
+  <si>
+    <t>0.9822,0.0073,0.0004,0.0043</t>
+  </si>
+  <si>
+    <t>0.9625,0.0105,0.0006,0.0126</t>
+  </si>
+  <si>
+    <t>0.9835,0.0075,0.0016,0.0032</t>
+  </si>
+  <si>
+    <t>0.9089,0.0037,0.0005,0.1103</t>
+  </si>
+  <si>
+    <t>0.9815,0.0073,0.0008,0.0043</t>
+  </si>
+  <si>
+    <t>0.9745,0.0125,0.0008,0.0044</t>
+  </si>
+  <si>
+    <t>0.9898,0.0014,0.0001,0.0056</t>
+  </si>
+  <si>
+    <t>0.9798,0.0062,0.0012,0.0059</t>
+  </si>
+  <si>
+    <t>0.5835,0.4353,0.0602,0.0330</t>
+  </si>
+  <si>
+    <t>0.8607,0.1944,0.0148,0.0024</t>
+  </si>
+  <si>
+    <t>0.1512,0.8578,0.0107,0.0063</t>
+  </si>
+  <si>
+    <t>0.0868,0.1032,0.9228,0.0020</t>
+  </si>
+  <si>
+    <t>0.8639,0.2406,0.0042,0.0017</t>
+  </si>
+  <si>
+    <t>0.9398,0.0472,0.0135,0.0045</t>
+  </si>
+  <si>
+    <t>0.9799,0.0126,0.0009,0.0028</t>
+  </si>
+  <si>
+    <t>0.9275,0.0900,0.0061,0.0038</t>
+  </si>
+  <si>
+    <t>0.0182,0.1025,0.9452,0.0021</t>
+  </si>
+  <si>
+    <t>0.9485,0.0510,0.0097,0.0019</t>
+  </si>
+  <si>
+    <t>0.0111,0.0929,0.9599,0.0090</t>
+  </si>
+  <si>
+    <t>0.0211,0.1214,0.9434,0.0067</t>
+  </si>
+  <si>
+    <t>0.0979,0.0185,0.9109,0.0184</t>
+  </si>
+  <si>
+    <t>0.0049,0.0992,0.9609,0.0109</t>
+  </si>
+  <si>
+    <t>0.0401,0.0644,0.9281,0.0070</t>
+  </si>
+  <si>
+    <t>0.0095,0.0092,0.9681,0.0324</t>
+  </si>
+  <si>
+    <t>0.0091,0.0051,0.9877,0.0036</t>
+  </si>
+  <si>
+    <t>0.4836,0.1184,0.4681,0.0651</t>
+  </si>
+  <si>
+    <t>0.4698,0.1480,0.4886,0.0100</t>
+  </si>
+  <si>
+    <t>0.5247,0.1690,0.2034,0.1337</t>
+  </si>
+  <si>
+    <t>0.3621,0.3572,0.3605,0.0327</t>
+  </si>
+  <si>
+    <t>0.2598,0.4879,0.3514,0.0213</t>
+  </si>
+  <si>
+    <t>0.4467,0.3214,0.2504,0.0741</t>
+  </si>
+  <si>
+    <t>0.3671,0.1892,0.5092,0.0833</t>
+  </si>
+  <si>
+    <t>0.4525,0.3752,0.2089,0.0268</t>
+  </si>
+  <si>
+    <t>0.9131,0.1052,0.0182,0.0026</t>
+  </si>
+  <si>
+    <t>0.7744,0.3306,0.0093,0.0016</t>
+  </si>
+  <si>
+    <t>0.9121,0.1159,0.0118,0.0026</t>
+  </si>
+  <si>
+    <t>0.9780,0.0270,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9306,0.0946,0.0019,0.0035</t>
+  </si>
+  <si>
+    <t>0.4893,0.1306,0.3636,0.1263</t>
+  </si>
+  <si>
+    <t>0.6064,0.0371,0.3295,0.0513</t>
+  </si>
+  <si>
+    <t>0.3170,0.0445,0.1098,0.5726</t>
+  </si>
+  <si>
+    <t>0.3603,0.2393,0.4469,0.0615</t>
+  </si>
+  <si>
+    <t>0.7401,0.0387,0.0482,0.0916</t>
+  </si>
+  <si>
+    <t>0.1225,0.1143,0.7634,0.0263</t>
+  </si>
+  <si>
+    <t>0.0167,0.0643,0.8932,0.0656</t>
+  </si>
+  <si>
+    <t>0.0061,0.0651,0.9749,0.0026</t>
+  </si>
+  <si>
+    <t>0.0655,0.1087,0.8632,0.0074</t>
+  </si>
+  <si>
+    <t>0.0279,0.2714,0.8822,0.0025</t>
+  </si>
+  <si>
+    <t>0.9868,0.0062,0.0007,0.0028</t>
+  </si>
+  <si>
+    <t>0.9831,0.0076,0.0033,0.0024</t>
+  </si>
+  <si>
+    <t>0.9701,0.0046,0.0004,0.0197</t>
+  </si>
+  <si>
+    <t>0.9919,0.0022,0.0006,0.0024</t>
+  </si>
+  <si>
+    <t>0.9763,0.0144,0.0019,0.0038</t>
+  </si>
+  <si>
+    <t>0.9831,0.0091,0.0022,0.0023</t>
+  </si>
+  <si>
+    <t>0.9905,0.0052,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9772,0.0127,0.0017,0.0041</t>
+  </si>
+  <si>
+    <t>0.0795,0.2219,0.7926,0.0035</t>
+  </si>
+  <si>
+    <t>0.4947,0.2936,0.2613,0.0140</t>
+  </si>
+  <si>
+    <t>0.3830,0.0085,0.0027,0.8067</t>
+  </si>
+  <si>
+    <t>0.0057,0.0469,0.9860,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0396,0.9942,0.0020</t>
+  </si>
+  <si>
+    <t>0.0677,0.1546,0.7954,0.0040</t>
+  </si>
+  <si>
+    <t>0.0041,0.0049,0.9873,0.0104</t>
+  </si>
+  <si>
+    <t>0.2208,0.1418,0.5992,0.0674</t>
+  </si>
+  <si>
+    <t>0.0021,0.0200,0.9851,0.0084</t>
+  </si>
+  <si>
+    <t>0.0062,0.0820,0.9674,0.0063</t>
+  </si>
+  <si>
+    <t>0.4414,0.1776,0.4192,0.1122</t>
+  </si>
+  <si>
+    <t>0.4895,0.0749,0.5424,0.0350</t>
+  </si>
+  <si>
+    <t>0.5134,0.0325,0.4872,0.0475</t>
+  </si>
+  <si>
+    <t>0.3681,0.0729,0.1878,0.3877</t>
+  </si>
+  <si>
+    <t>0.9510,0.0506,0.0043,0.0035</t>
+  </si>
+  <si>
+    <t>0.9839,0.0092,0.0013,0.0021</t>
+  </si>
+  <si>
+    <t>0.9918,0.0029,0.0002,0.0018</t>
+  </si>
+  <si>
+    <t>0.9879,0.0046,0.0008,0.0022</t>
+  </si>
+  <si>
+    <t>0.9883,0.0061,0.0008,0.0021</t>
+  </si>
+  <si>
+    <t>0.9832,0.0184,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.9853,0.0092,0.0023,0.0014</t>
+  </si>
+  <si>
+    <t>0.9898,0.0037,0.0007,0.0026</t>
+  </si>
+  <si>
+    <t>0.0289,0.1947,0.8874,0.0080</t>
+  </si>
+  <si>
+    <t>0.0070,0.0757,0.9714,0.0035</t>
+  </si>
+  <si>
+    <t>0.0025,0.0186,0.9827,0.0138</t>
+  </si>
+  <si>
+    <t>0.0979,0.0688,0.8436,0.0168</t>
+  </si>
+  <si>
+    <t>0.0125,0.0166,0.9731,0.0111</t>
+  </si>
+  <si>
+    <t>0.0585,0.0511,0.6570,0.3815</t>
+  </si>
+  <si>
+    <t>0.1141,0.0344,0.8522,0.0340</t>
+  </si>
+  <si>
+    <t>0.0123,0.0755,0.9001,0.0446</t>
+  </si>
+  <si>
+    <t>0.4857,0.0088,0.0910,0.4453</t>
+  </si>
+  <si>
+    <t>0.0263,0.0081,0.0004,0.9894</t>
+  </si>
+  <si>
+    <t>0.0103,0.0106,0.0022,0.9930</t>
+  </si>
+  <si>
+    <t>0.0013,0.0016,0.0010,0.9986</t>
+  </si>
+  <si>
+    <t>0.0024,0.0016,0.0005,0.9985</t>
+  </si>
+  <si>
+    <t>0.3547,0.0371,0.0115,0.6778</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2147,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2315,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3113,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3575,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,10 +3897,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,10 +4191,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,10 +4793,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,10 +5059,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,10 +5213,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
